--- a/main/ig/StructureDefinition-fr-core-organization-sae-category.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-sae-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-sae-category.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-sae-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-sae-category.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-sae-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-sae-category.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-sae-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-sae-category.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-sae-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-sae-category.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-sae-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-organization-sae-category.xlsx
+++ b/main/ig/StructureDefinition-fr-core-organization-sae-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
